--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,736 +413,690 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>16.88121</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.7954</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.80319</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.42007</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.82649</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.97702</v>
+        <v>16.72052</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31008</v>
+        <v>16.55649</v>
       </c>
       <c r="E3" t="n">
-        <v>17.05043</v>
+        <v>16.67219</v>
       </c>
       <c r="F3" t="n">
-        <v>43.73041</v>
+        <v>42.56367</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05118</v>
+        <v>0.05068</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83523</v>
+        <v>1.8145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.67263</v>
+        <v>16.97229</v>
       </c>
       <c r="D4" t="n">
-        <v>16.77765</v>
+        <v>16.63259</v>
       </c>
       <c r="E4" t="n">
-        <v>16.6334</v>
+        <v>16.81877</v>
       </c>
       <c r="F4" t="n">
-        <v>43.06329</v>
+        <v>41.8297</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05007</v>
+        <v>0.0505</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80497</v>
+        <v>1.87059</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.69723</v>
+        <v>16.51581</v>
       </c>
       <c r="D5" t="n">
-        <v>16.8109</v>
+        <v>16.41176</v>
       </c>
       <c r="E5" t="n">
-        <v>16.56628</v>
+        <v>16.47552</v>
       </c>
       <c r="F5" t="n">
-        <v>43.16644</v>
+        <v>42.03832</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05094</v>
+        <v>0.04992</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8403</v>
+        <v>1.84952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.82181</v>
+        <v>16.79908</v>
       </c>
       <c r="D6" t="n">
-        <v>16.86427</v>
+        <v>16.42877</v>
       </c>
       <c r="E6" t="n">
-        <v>16.79036</v>
+        <v>16.77741</v>
       </c>
       <c r="F6" t="n">
-        <v>43.11013</v>
+        <v>42.95392</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05064</v>
+        <v>0.04973</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81458</v>
+        <v>1.86005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.11875</v>
+        <v>17.28393</v>
       </c>
       <c r="D7" t="n">
-        <v>16.42954</v>
+        <v>16.78751</v>
       </c>
       <c r="E7" t="n">
-        <v>16.55217</v>
+        <v>16.82298</v>
       </c>
       <c r="F7" t="n">
-        <v>42.36631</v>
+        <v>42.18375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0505</v>
+        <v>0.05115</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84097</v>
+        <v>1.81455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.97431</v>
+        <v>17.02025</v>
       </c>
       <c r="D8" t="n">
-        <v>16.87213</v>
+        <v>16.4219</v>
       </c>
       <c r="E8" t="n">
-        <v>16.83578</v>
+        <v>16.54553</v>
       </c>
       <c r="F8" t="n">
-        <v>43.21973</v>
+        <v>42.246</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05088</v>
+        <v>0.05125</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8315</v>
+        <v>1.80723</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.69794</v>
+        <v>17.06102</v>
       </c>
       <c r="D9" t="n">
-        <v>16.32931</v>
+        <v>16.70915</v>
       </c>
       <c r="E9" t="n">
-        <v>16.44432</v>
+        <v>16.86938</v>
       </c>
       <c r="F9" t="n">
-        <v>42.41424</v>
+        <v>42.56121</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05089</v>
+        <v>0.05142</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82563</v>
+        <v>1.83168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.91881</v>
+        <v>17.03877</v>
       </c>
       <c r="D10" t="n">
-        <v>16.98872</v>
+        <v>16.60923</v>
       </c>
       <c r="E10" t="n">
-        <v>16.73006</v>
+        <v>16.63363</v>
       </c>
       <c r="F10" t="n">
-        <v>42.41535</v>
+        <v>43.31251</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05003</v>
+        <v>0.05009</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79483</v>
+        <v>1.80569</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.56579</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.5224</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.73991</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41.90499</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.81261</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.61038</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.121</v>
+          <t>Unit 8</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.6137</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.10097</v>
+          <t>Unit 9</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.60415</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.10046</v>
+          <t>Unit 4</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.61324</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.09712</v>
+          <t>Unit 5</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.61064</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.12329</v>
+          <t>Unit 6</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.61387</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.12496</v>
+          <t>Unit 1</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.6202800000000001</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.07567</v>
+          <t>Unit 2</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.60187</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.1031</v>
+          <t>Unit 3</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6123</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.10983</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7464499999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.61366</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.97142</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.11111</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.09467</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.12721</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.76642</v>
+        <v>0.75295</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08221000000000001</v>
+        <v>0.08047</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60686</v>
+        <v>0.59741</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9479</v>
+        <v>0.94679</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10896</v>
+        <v>0.10907</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00754</v>
+        <v>0.00763</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09402000000000001</v>
+        <v>0.09331</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12759</v>
+        <v>0.1274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.73966</v>
+        <v>0.76656</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07943</v>
+        <v>0.08112</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6004699999999999</v>
+        <v>0.60593</v>
       </c>
       <c r="F24" t="n">
-        <v>0.96628</v>
+        <v>0.9506</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10858</v>
+        <v>0.10769</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00753</v>
+        <v>0.00748</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.09268999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12543</v>
+        <v>0.12682</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.76058</v>
+        <v>0.73833</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07892</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60092</v>
+        <v>0.6042</v>
       </c>
       <c r="F25" t="n">
-        <v>0.96716</v>
+        <v>0.96643</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10889</v>
+        <v>0.11006</v>
       </c>
       <c r="H25" t="n">
         <v>0.00767</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09363</v>
+        <v>0.09208</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12798</v>
+        <v>0.12586</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74869</v>
+        <v>0.74031</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0803</v>
+        <v>0.08176</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60907</v>
+        <v>0.59843</v>
       </c>
       <c r="F26" t="n">
-        <v>0.95292</v>
+        <v>0.96685</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10924</v>
+        <v>0.11029</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00758</v>
+        <v>0.00767</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09353</v>
+        <v>0.09408999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1251</v>
+        <v>0.12923</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.75338</v>
+        <v>0.7236399999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08187</v>
+        <v>0.08025</v>
       </c>
       <c r="E27" t="n">
-        <v>0.60241</v>
+        <v>0.6016899999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.94536</v>
+        <v>0.96948</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10792</v>
+        <v>0.10897</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00762</v>
+        <v>0.00777</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09273000000000001</v>
+        <v>0.09454</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12645</v>
+        <v>0.12643</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74743</v>
+        <v>0.73836</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08248999999999999</v>
+        <v>0.08071</v>
       </c>
       <c r="E28" t="n">
-        <v>0.61468</v>
+        <v>0.60294</v>
       </c>
       <c r="F28" t="n">
-        <v>0.97168</v>
+        <v>0.9708599999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1106</v>
+        <v>0.11023</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00762</v>
+        <v>0.0075</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09222</v>
+        <v>0.09134</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12757</v>
+        <v>0.1251</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.73997</v>
+        <v>0.75268</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08005</v>
+        <v>0.08043</v>
       </c>
       <c r="E29" t="n">
-        <v>0.59724</v>
+        <v>0.60226</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.95314</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10876</v>
+        <v>0.10837</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00763</v>
+        <v>0.00771</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09143999999999999</v>
+        <v>0.09075</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12501</v>
+        <v>0.12519</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.75818</v>
+        <v>0.75337</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07988000000000001</v>
+        <v>0.08066</v>
       </c>
       <c r="E30" t="n">
-        <v>0.60275</v>
+        <v>0.61331</v>
       </c>
       <c r="F30" t="n">
-        <v>0.94919</v>
+        <v>0.96679</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10945</v>
+        <v>0.11057</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00768</v>
+        <v>0.00759</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09347999999999999</v>
+        <v>0.09234000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12725</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.73219</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08087</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.61299</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.96363</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.10959</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.09467</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.12587</v>
+        <v>0.12689</v>
       </c>
     </row>
   </sheetData>
